--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35964-2026 artfynd.xlsx
+++ b/artfynd/A 35964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136686177</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
